--- a/dynamics/src/dynamics/xlsx/ur_dynamics_limit_torque_calc.xlsx
+++ b/dynamics/src/dynamics/xlsx/ur_dynamics_limit_torque_calc.xlsx
@@ -480,19 +480,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>29.5609375358765</v>
+        <v>34.37844471301438</v>
       </c>
       <c r="B2" t="n">
-        <v>-200.3470077112426</v>
+        <v>-145.7425941717929</v>
       </c>
       <c r="C2" t="n">
-        <v>-86.6543467639719</v>
+        <v>-57.23978347980592</v>
       </c>
       <c r="D2" t="n">
-        <v>-22.00713310542239</v>
+        <v>-9.983765136300836</v>
       </c>
       <c r="E2" t="n">
-        <v>3.249228935549836</v>
+        <v>1.660025162470542</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -518,19 +518,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-7.554328338420116</v>
+        <v>-19.84552557895821</v>
       </c>
       <c r="B3" t="n">
-        <v>53.65728116527465</v>
+        <v>122.9517974776907</v>
       </c>
       <c r="C3" t="n">
-        <v>36.57771034042356</v>
+        <v>28.38673012326081</v>
       </c>
       <c r="D3" t="n">
-        <v>24.37278933389817</v>
+        <v>9.213564577440827</v>
       </c>
       <c r="E3" t="n">
-        <v>2.083742322318324</v>
+        <v>1.991485696535491</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -539,36 +539,36 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J3" t="n">
         <v>180</v>
       </c>
       <c r="K3" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20.91111093978237</v>
+        <v>20.39499856561554</v>
       </c>
       <c r="B4" t="n">
-        <v>273.6163981686916</v>
+        <v>216.5406411005748</v>
       </c>
       <c r="C4" t="n">
-        <v>120.8607164439623</v>
+        <v>88.00677402733466</v>
       </c>
       <c r="D4" t="n">
-        <v>28.66631718251178</v>
+        <v>7.169532643124927</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.684620300962077</v>
+        <v>2.071802748594044</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -583,10 +583,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="K4" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="L4" t="n">
         <v>90</v>
@@ -594,19 +594,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20.02618696264082</v>
+        <v>13.82188411759142</v>
       </c>
       <c r="B5" t="n">
-        <v>-204.4410887927621</v>
+        <v>-158.8673436257959</v>
       </c>
       <c r="C5" t="n">
-        <v>-86.12283339305139</v>
+        <v>-56.36165188165983</v>
       </c>
       <c r="D5" t="n">
-        <v>-17.99482123350187</v>
+        <v>3.95678961405</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.556335527851106</v>
+        <v>3.777635410861072</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -624,7 +624,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="L5" t="n">
         <v>90</v>
@@ -632,19 +632,19 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20.91111093978237</v>
+        <v>14.5199742077884</v>
       </c>
       <c r="B6" t="n">
-        <v>273.6163981686916</v>
+        <v>72.02675336725372</v>
       </c>
       <c r="C6" t="n">
-        <v>120.8607164439623</v>
+        <v>89.51105667811771</v>
       </c>
       <c r="D6" t="n">
-        <v>28.66631718251179</v>
+        <v>8.67381529390798</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.684620300962077</v>
+        <v>2.573230298855061</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -653,16 +653,16 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J6" t="n">
-        <v>-180</v>
+        <v>-90</v>
       </c>
       <c r="K6" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="L6" t="n">
         <v>90</v>
@@ -670,19 +670,19 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4.340761864047955</v>
+        <v>5.825234636309028</v>
       </c>
       <c r="B7" t="n">
-        <v>32.97931957050644</v>
+        <v>39.54505058413642</v>
       </c>
       <c r="C7" t="n">
-        <v>-97.21930465928428</v>
+        <v>-69.86530631344375</v>
       </c>
       <c r="D7" t="n">
-        <v>-21.44266583093474</v>
+        <v>-5.597555995224017</v>
       </c>
       <c r="E7" t="n">
-        <v>0.86359919126176</v>
+        <v>-0.6942699605749733</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -697,10 +697,10 @@
         <v>180</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="K7" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="L7" t="n">
         <v>90</v>
@@ -708,19 +708,19 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16.94030854796732</v>
+        <v>6.290693894727911</v>
       </c>
       <c r="B8" t="n">
-        <v>268.0264370117421</v>
+        <v>204.2411610186128</v>
       </c>
       <c r="C8" t="n">
-        <v>119.8963497394528</v>
+        <v>85.54397553039968</v>
       </c>
       <c r="D8" t="n">
-        <v>31.18274897900232</v>
+        <v>13.88276704960477</v>
       </c>
       <c r="E8" t="n">
-        <v>2.561403643347621</v>
+        <v>0.7710556663427746</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -746,19 +746,19 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5.539137440968354</v>
+        <v>16.47871246661876</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4432797967029953</v>
+        <v>191.0145523346762</v>
       </c>
       <c r="C9" t="n">
-        <v>-16.0981289244154</v>
+        <v>65.64402962803598</v>
       </c>
       <c r="D9" t="n">
-        <v>-27.34521199207841</v>
+        <v>-12.24232311127374</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3867432134851307</v>
+        <v>-1.629771564464919</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -784,19 +784,19 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>19.13376223149632</v>
+        <v>5.097786373893292</v>
       </c>
       <c r="B10" t="n">
-        <v>266.7695077191397</v>
+        <v>21.37052508711229</v>
       </c>
       <c r="C10" t="n">
-        <v>115.6628283047832</v>
+        <v>14.93595863420942</v>
       </c>
       <c r="D10" t="n">
-        <v>24.70931706953304</v>
+        <v>11.32690221381423</v>
       </c>
       <c r="E10" t="n">
-        <v>29.14287530910124</v>
+        <v>10.81752132817981</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -805,13 +805,13 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>180</v>
@@ -822,19 +822,19 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>19.64047272204029</v>
+        <v>8.686653590311378</v>
       </c>
       <c r="B11" t="n">
-        <v>261.9231818685554</v>
+        <v>34.7433528960677</v>
       </c>
       <c r="C11" t="n">
-        <v>113.2364371733118</v>
+        <v>21.28880073951058</v>
       </c>
       <c r="D11" t="n">
-        <v>24.10394704776197</v>
+        <v>11.13123309188577</v>
       </c>
       <c r="E11" t="n">
-        <v>-28.3580369340591</v>
+        <v>-10.57115926597914</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -843,13 +843,13 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -968,19 +968,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>29.5609375358765</v>
+        <v>34.37844471301438</v>
       </c>
       <c r="B15" t="n">
-        <v>273.6163981686916</v>
+        <v>216.5406411005748</v>
       </c>
       <c r="C15" t="n">
-        <v>120.8607164439623</v>
+        <v>89.51105667811771</v>
       </c>
       <c r="D15" t="n">
-        <v>31.18274897900232</v>
+        <v>13.88276704960477</v>
       </c>
       <c r="E15" t="n">
-        <v>29.14287530910124</v>
+        <v>10.81752132817981</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
